--- a/public/templates/背书统计导入模板.xlsx
+++ b/public/templates/背书统计导入模板.xlsx
@@ -425,13 +425,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
